--- a/invoice_report.xlsx
+++ b/invoice_report.xlsx
@@ -413,9 +413,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Invoice ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Invoice Number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Invoice Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GSTIN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DEMO Sliced Invoices</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>INV-3337</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>January 25, 2016</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AZ 12345</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>93.50</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEMO Sliced Invoices</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INV-3337</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>January 25, 2016</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AZ 12345</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>93.50</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>